--- a/vtiger-crm-hybrid-automation-framework-m1/src/test/resources/testscriptdata.xlsx
+++ b/vtiger-crm-hybrid-automation-framework-m1/src/test/resources/testscriptdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>orgName</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Chaudhary</t>
+  </si>
+  <si>
+    <t>89</t>
   </si>
 </sst>
 </file>
@@ -110,10 +113,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,33 +398,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
